--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251206_201414.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
